--- a/output/mariners_report_20260705.xlsx
+++ b/output/mariners_report_20260705.xlsx
@@ -149,7 +149,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -284,9 +284,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="6" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="6" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -2890,78 +2887,78 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="30" t="inlineStr">
+      <c r="A46" s="15" t="inlineStr">
         <is>
           <t>Michael Rucker</t>
         </is>
       </c>
-      <c r="B46" s="32" t="inlineStr">
+      <c r="B46" s="17" t="inlineStr">
         <is>
           <t>RP</t>
         </is>
       </c>
-      <c r="C46" s="31" t="inlineStr">
-        <is>
-          <t>DFA</t>
-        </is>
-      </c>
-      <c r="D46" s="35" t="n">
+      <c r="C46" s="16" t="inlineStr">
+        <is>
+          <t>Below Average</t>
+        </is>
+      </c>
+      <c r="D46" s="20" t="n">
         <v>8.1</v>
       </c>
-      <c r="E46" s="46" t="n">
+      <c r="E46" s="44" t="n">
         <v>6.48</v>
       </c>
-      <c r="F46" s="33" t="n">
+      <c r="F46" s="18" t="n">
         <v>1.32</v>
       </c>
-      <c r="G46" s="35" t="n">
+      <c r="G46" s="20" t="n">
         <v>12.2</v>
       </c>
-      <c r="H46" s="33" t="n"/>
-      <c r="I46" s="34" t="n"/>
-      <c r="J46" s="35" t="n">
+      <c r="H46" s="18" t="n"/>
+      <c r="I46" s="42" t="n"/>
+      <c r="J46" s="20" t="n">
         <v>-0.1</v>
       </c>
-      <c r="K46" s="31" t="inlineStr">
-        <is>
-          <t>DFA — below replacement level</t>
+      <c r="K46" s="16" t="inlineStr">
+        <is>
+          <t>Consider replacement</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="21" t="inlineStr">
+      <c r="A47" s="15" t="inlineStr">
         <is>
           <t>Domingo González</t>
         </is>
       </c>
-      <c r="B47" s="8" t="inlineStr">
+      <c r="B47" s="17" t="inlineStr">
         <is>
           <t>RP</t>
         </is>
       </c>
-      <c r="C47" s="22" t="inlineStr">
-        <is>
-          <t>Small sample</t>
-        </is>
-      </c>
-      <c r="D47" s="24" t="n">
+      <c r="C47" s="16" t="inlineStr">
+        <is>
+          <t>Below Average</t>
+        </is>
+      </c>
+      <c r="D47" s="20" t="n">
         <v>7.2</v>
       </c>
-      <c r="E47" s="47" t="n">
+      <c r="E47" s="44" t="n">
         <v>4.7</v>
       </c>
-      <c r="F47" s="23" t="n">
+      <c r="F47" s="18" t="n">
         <v>1.826</v>
       </c>
-      <c r="G47" s="24" t="n">
+      <c r="G47" s="20" t="n">
         <v>6.2</v>
       </c>
-      <c r="H47" s="23" t="n"/>
-      <c r="I47" s="36" t="n"/>
-      <c r="J47" s="24" t="n"/>
-      <c r="K47" s="22" t="inlineStr">
-        <is>
-          <t>Monitor</t>
+      <c r="H47" s="18" t="n"/>
+      <c r="I47" s="42" t="n"/>
+      <c r="J47" s="20" t="n"/>
+      <c r="K47" s="16" t="inlineStr">
+        <is>
+          <t>Consider replacement</t>
         </is>
       </c>
     </row>
@@ -2984,7 +2981,7 @@
       <c r="D48" s="24" t="n">
         <v>3</v>
       </c>
-      <c r="E48" s="47" t="n">
+      <c r="E48" s="46" t="n">
         <v>9</v>
       </c>
       <c r="F48" s="23" t="n">
@@ -3023,7 +3020,7 @@
       <c r="D49" s="24" t="n">
         <v>2</v>
       </c>
-      <c r="E49" s="47" t="n">
+      <c r="E49" s="46" t="n">
         <v>4.5</v>
       </c>
       <c r="F49" s="23" t="n">
@@ -3141,7 +3138,7 @@
       <c r="B4" s="7" t="n">
         <v>45</v>
       </c>
-      <c r="C4" s="48" t="n">
+      <c r="C4" s="47" t="n">
         <v>0.35</v>
       </c>
       <c r="D4" s="40" t="n">
@@ -3150,16 +3147,16 @@
       <c r="E4" s="19" t="n">
         <v>-0.04</v>
       </c>
-      <c r="F4" s="49" t="n">
+      <c r="F4" s="48" t="n">
         <v>6.1</v>
       </c>
-      <c r="G4" s="49" t="n">
+      <c r="G4" s="48" t="n">
         <v>48.5</v>
       </c>
-      <c r="H4" s="49" t="n">
+      <c r="H4" s="48" t="n">
         <v>100.635807059</v>
       </c>
-      <c r="I4" s="49" t="n">
+      <c r="I4" s="48" t="n">
         <v>15.6</v>
       </c>
     </row>
@@ -3172,7 +3169,7 @@
       <c r="B5" s="7" t="n">
         <v>177</v>
       </c>
-      <c r="C5" s="48" t="n">
+      <c r="C5" s="47" t="n">
         <v>0.375</v>
       </c>
       <c r="D5" s="23" t="n">
@@ -3181,16 +3178,16 @@
       <c r="E5" s="36" t="n">
         <v>-0.002</v>
       </c>
-      <c r="F5" s="49" t="n">
+      <c r="F5" s="48" t="n">
         <v>19.2</v>
       </c>
-      <c r="G5" s="49" t="n">
+      <c r="G5" s="48" t="n">
         <v>47.1</v>
       </c>
-      <c r="H5" s="49" t="n">
+      <c r="H5" s="48" t="n">
         <v>102.550571765</v>
       </c>
-      <c r="I5" s="49" t="n">
+      <c r="I5" s="48" t="n">
         <v>32.8</v>
       </c>
     </row>
@@ -3203,7 +3200,7 @@
       <c r="B6" s="7" t="n">
         <v>39</v>
       </c>
-      <c r="C6" s="48" t="n">
+      <c r="C6" s="47" t="n">
         <v>0.296</v>
       </c>
       <c r="D6" s="40" t="n">
@@ -3212,16 +3209,16 @@
       <c r="E6" s="19" t="n">
         <v>-0.073</v>
       </c>
-      <c r="F6" s="49" t="n">
+      <c r="F6" s="48" t="n">
         <v>9.1</v>
       </c>
-      <c r="G6" s="49" t="n">
+      <c r="G6" s="48" t="n">
         <v>45.5</v>
       </c>
-      <c r="H6" s="49" t="n">
+      <c r="H6" s="48" t="n">
         <v>100.621557273</v>
       </c>
-      <c r="I6" s="49" t="n">
+      <c r="I6" s="48" t="n">
         <v>28.2</v>
       </c>
     </row>
@@ -3234,7 +3231,7 @@
       <c r="B7" s="7" t="n">
         <v>148</v>
       </c>
-      <c r="C7" s="48" t="n">
+      <c r="C7" s="47" t="n">
         <v>0.365</v>
       </c>
       <c r="D7" s="23" t="n">
@@ -3243,16 +3240,16 @@
       <c r="E7" s="36" t="n">
         <v>0</v>
       </c>
-      <c r="F7" s="49" t="n">
+      <c r="F7" s="48" t="n">
         <v>15.8</v>
       </c>
-      <c r="G7" s="49" t="n">
+      <c r="G7" s="48" t="n">
         <v>49.5</v>
       </c>
-      <c r="H7" s="49" t="n">
+      <c r="H7" s="48" t="n">
         <v>103.862953922</v>
       </c>
-      <c r="I7" s="49" t="n">
+      <c r="I7" s="48" t="n">
         <v>21.6</v>
       </c>
     </row>
@@ -3265,7 +3262,7 @@
       <c r="B8" s="7" t="n">
         <v>231</v>
       </c>
-      <c r="C8" s="48" t="n">
+      <c r="C8" s="47" t="n">
         <v>0.342</v>
       </c>
       <c r="D8" s="23" t="n">
@@ -3274,16 +3271,16 @@
       <c r="E8" s="36" t="n">
         <v>-0.012</v>
       </c>
-      <c r="F8" s="49" t="n">
+      <c r="F8" s="48" t="n">
         <v>9.5</v>
       </c>
-      <c r="G8" s="49" t="n">
+      <c r="G8" s="48" t="n">
         <v>36.9</v>
       </c>
-      <c r="H8" s="49" t="n">
+      <c r="H8" s="48" t="n">
         <v>98.715012192</v>
       </c>
-      <c r="I8" s="49" t="n">
+      <c r="I8" s="48" t="n">
         <v>19</v>
       </c>
     </row>
@@ -3296,7 +3293,7 @@
       <c r="B9" s="7" t="n">
         <v>101</v>
       </c>
-      <c r="C9" s="48" t="n">
+      <c r="C9" s="47" t="n">
         <v>0.374</v>
       </c>
       <c r="D9" s="33" t="n">
@@ -3305,16 +3302,16 @@
       <c r="E9" s="34" t="n">
         <v>0.029</v>
       </c>
-      <c r="F9" s="49" t="n">
+      <c r="F9" s="48" t="n">
         <v>4.4</v>
       </c>
-      <c r="G9" s="49" t="n">
+      <c r="G9" s="48" t="n">
         <v>32.9</v>
       </c>
-      <c r="H9" s="49" t="n">
+      <c r="H9" s="48" t="n">
         <v>96.905916471</v>
       </c>
-      <c r="I9" s="49" t="n">
+      <c r="I9" s="48" t="n">
         <v>14.9</v>
       </c>
     </row>
@@ -3327,7 +3324,7 @@
       <c r="B10" s="7" t="n">
         <v>268</v>
       </c>
-      <c r="C10" s="48" t="n">
+      <c r="C10" s="47" t="n">
         <v>0.357</v>
       </c>
       <c r="D10" s="23" t="n">
@@ -3336,16 +3333,16 @@
       <c r="E10" s="36" t="n">
         <v>0.016</v>
       </c>
-      <c r="F10" s="49" t="n">
+      <c r="F10" s="48" t="n">
         <v>7.5</v>
       </c>
-      <c r="G10" s="49" t="n">
+      <c r="G10" s="48" t="n">
         <v>41.4</v>
       </c>
-      <c r="H10" s="49" t="n">
+      <c r="H10" s="48" t="n">
         <v>100.274056207</v>
       </c>
-      <c r="I10" s="49" t="n">
+      <c r="I10" s="48" t="n">
         <v>22.8</v>
       </c>
     </row>
@@ -3358,7 +3355,7 @@
       <c r="B11" s="7" t="n">
         <v>276</v>
       </c>
-      <c r="C11" s="48" t="n">
+      <c r="C11" s="47" t="n">
         <v>0.337</v>
       </c>
       <c r="D11" s="23" t="n">
@@ -3367,16 +3364,16 @@
       <c r="E11" s="36" t="n">
         <v>0</v>
       </c>
-      <c r="F11" s="49" t="n">
+      <c r="F11" s="48" t="n">
         <v>9.699999999999999</v>
       </c>
-      <c r="G11" s="49" t="n">
+      <c r="G11" s="48" t="n">
         <v>42.9</v>
       </c>
-      <c r="H11" s="49" t="n">
+      <c r="H11" s="48" t="n">
         <v>102.739286531</v>
       </c>
-      <c r="I11" s="49" t="n">
+      <c r="I11" s="48" t="n">
         <v>21.4</v>
       </c>
     </row>
@@ -3389,7 +3386,7 @@
       <c r="B12" s="7" t="n">
         <v>251</v>
       </c>
-      <c r="C12" s="48" t="n">
+      <c r="C12" s="47" t="n">
         <v>0.296</v>
       </c>
       <c r="D12" s="40" t="n">
@@ -3398,16 +3395,16 @@
       <c r="E12" s="19" t="n">
         <v>-0.033</v>
       </c>
-      <c r="F12" s="49" t="n">
+      <c r="F12" s="48" t="n">
         <v>5.6</v>
       </c>
-      <c r="G12" s="49" t="n">
+      <c r="G12" s="48" t="n">
         <v>37.8</v>
       </c>
-      <c r="H12" s="49" t="n">
+      <c r="H12" s="48" t="n">
         <v>98.83080898</v>
       </c>
-      <c r="I12" s="49" t="n">
+      <c r="I12" s="48" t="n">
         <v>13.1</v>
       </c>
     </row>
@@ -3420,7 +3417,7 @@
       <c r="B13" s="7" t="n">
         <v>249</v>
       </c>
-      <c r="C13" s="48" t="n">
+      <c r="C13" s="47" t="n">
         <v>0.307</v>
       </c>
       <c r="D13" s="40" t="n">
@@ -3429,16 +3426,16 @@
       <c r="E13" s="19" t="n">
         <v>-0.022</v>
       </c>
-      <c r="F13" s="49" t="n">
+      <c r="F13" s="48" t="n">
         <v>5.8</v>
       </c>
-      <c r="G13" s="49" t="n">
+      <c r="G13" s="48" t="n">
         <v>37</v>
       </c>
-      <c r="H13" s="49" t="n">
+      <c r="H13" s="48" t="n">
         <v>98.785526977</v>
       </c>
-      <c r="I13" s="49" t="n">
+      <c r="I13" s="48" t="n">
         <v>20.5</v>
       </c>
     </row>
@@ -3451,7 +3448,7 @@
       <c r="B14" s="7" t="n">
         <v>91</v>
       </c>
-      <c r="C14" s="48" t="n">
+      <c r="C14" s="47" t="n">
         <v>0.296</v>
       </c>
       <c r="D14" s="23" t="n">
@@ -3460,16 +3457,16 @@
       <c r="E14" s="36" t="n">
         <v>0.001</v>
       </c>
-      <c r="F14" s="49" t="n">
+      <c r="F14" s="48" t="n">
         <v>6.3</v>
       </c>
-      <c r="G14" s="49" t="n">
+      <c r="G14" s="48" t="n">
         <v>54.2</v>
       </c>
-      <c r="H14" s="49" t="n">
+      <c r="H14" s="48" t="n">
         <v>101.464692917</v>
       </c>
-      <c r="I14" s="49" t="n">
+      <c r="I14" s="48" t="n">
         <v>29.7</v>
       </c>
     </row>
@@ -3482,7 +3479,7 @@
       <c r="B15" s="7" t="n">
         <v>181</v>
       </c>
-      <c r="C15" s="48" t="n">
+      <c r="C15" s="47" t="n">
         <v>0.253</v>
       </c>
       <c r="D15" s="40" t="n">
@@ -3491,16 +3488,16 @@
       <c r="E15" s="19" t="n">
         <v>-0.036</v>
       </c>
-      <c r="F15" s="49" t="n">
+      <c r="F15" s="48" t="n">
         <v>12.3</v>
       </c>
-      <c r="G15" s="49" t="n">
+      <c r="G15" s="48" t="n">
         <v>31.1</v>
       </c>
-      <c r="H15" s="49" t="n">
+      <c r="H15" s="48" t="n">
         <v>98.783037736</v>
       </c>
-      <c r="I15" s="49" t="n">
+      <c r="I15" s="48" t="n">
         <v>31.5</v>
       </c>
     </row>
@@ -3513,7 +3510,7 @@
       <c r="B16" s="7" t="n">
         <v>19</v>
       </c>
-      <c r="C16" s="48" t="n">
+      <c r="C16" s="47" t="n">
         <v>0.261</v>
       </c>
       <c r="D16" s="23" t="n">
@@ -3522,16 +3519,16 @@
       <c r="E16" s="36" t="n">
         <v>-0.002</v>
       </c>
-      <c r="F16" s="49" t="n">
+      <c r="F16" s="48" t="n">
         <v>20</v>
       </c>
-      <c r="G16" s="49" t="n">
+      <c r="G16" s="48" t="n">
         <v>70</v>
       </c>
-      <c r="H16" s="49" t="n">
+      <c r="H16" s="48" t="n">
         <v>103.735736</v>
       </c>
-      <c r="I16" s="49" t="n">
+      <c r="I16" s="48" t="n">
         <v>42.1</v>
       </c>
     </row>
@@ -3544,7 +3541,7 @@
       <c r="B17" s="7" t="n">
         <v>57</v>
       </c>
-      <c r="C17" s="48" t="n">
+      <c r="C17" s="47" t="n">
         <v>0.38</v>
       </c>
       <c r="D17" s="33" t="n">
@@ -3553,16 +3550,16 @@
       <c r="E17" s="34" t="n">
         <v>0.118</v>
       </c>
-      <c r="F17" s="49" t="n">
+      <c r="F17" s="48" t="n">
         <v>5.7</v>
       </c>
-      <c r="G17" s="49" t="n">
+      <c r="G17" s="48" t="n">
         <v>37.1</v>
       </c>
-      <c r="H17" s="49" t="n">
+      <c r="H17" s="48" t="n">
         <v>98.536972941</v>
       </c>
-      <c r="I17" s="49" t="n">
+      <c r="I17" s="48" t="n">
         <v>28.1</v>
       </c>
     </row>
@@ -3575,7 +3572,7 @@
       <c r="B18" s="7" t="n">
         <v>90</v>
       </c>
-      <c r="C18" s="48" t="n">
+      <c r="C18" s="47" t="n">
         <v>0.192</v>
       </c>
       <c r="D18" s="40" t="n">
@@ -3584,16 +3581,16 @@
       <c r="E18" s="19" t="n">
         <v>-0.062</v>
       </c>
-      <c r="F18" s="49" t="n">
+      <c r="F18" s="48" t="n">
         <v>9.1</v>
       </c>
-      <c r="G18" s="49" t="n">
+      <c r="G18" s="48" t="n">
         <v>36.4</v>
       </c>
-      <c r="H18" s="49" t="n">
+      <c r="H18" s="48" t="n">
         <v>98.34696964299999</v>
       </c>
-      <c r="I18" s="49" t="n">
+      <c r="I18" s="48" t="n">
         <v>30</v>
       </c>
     </row>
@@ -3606,7 +3603,7 @@
       <c r="B19" s="7" t="n">
         <v>120</v>
       </c>
-      <c r="C19" s="48" t="n">
+      <c r="C19" s="47" t="n">
         <v>0.219</v>
       </c>
       <c r="D19" s="23" t="n">
@@ -3615,16 +3612,16 @@
       <c r="E19" s="36" t="n">
         <v>-0.02</v>
       </c>
-      <c r="F19" s="49" t="n">
+      <c r="F19" s="48" t="n">
         <v>1.5</v>
       </c>
-      <c r="G19" s="49" t="n">
+      <c r="G19" s="48" t="n">
         <v>13.6</v>
       </c>
-      <c r="H19" s="49" t="n">
+      <c r="H19" s="48" t="n">
         <v>93.39903750000001</v>
       </c>
-      <c r="I19" s="49" t="n">
+      <c r="I19" s="48" t="n">
         <v>30</v>
       </c>
     </row>
@@ -3691,7 +3688,7 @@
       <c r="B23" s="7" t="n">
         <v>79</v>
       </c>
-      <c r="C23" s="48" t="n">
+      <c r="C23" s="47" t="n">
         <v>0.238</v>
       </c>
       <c r="D23" s="23" t="n">
@@ -3700,16 +3697,16 @@
       <c r="E23" s="36" t="n">
         <v>0.017</v>
       </c>
-      <c r="F23" s="49" t="n">
+      <c r="F23" s="48" t="n">
         <v>25.3</v>
       </c>
-      <c r="G23" s="49" t="n">
+      <c r="G23" s="48" t="n">
         <v>29.3</v>
       </c>
-      <c r="H23" s="49" t="n">
+      <c r="H23" s="48" t="n">
         <v>25</v>
       </c>
-      <c r="I23" s="49" t="n">
+      <c r="I23" s="48" t="n">
         <v>3.6</v>
       </c>
     </row>
@@ -3722,7 +3719,7 @@
       <c r="B24" s="7" t="n">
         <v>117</v>
       </c>
-      <c r="C24" s="48" t="n">
+      <c r="C24" s="47" t="n">
         <v>0.295</v>
       </c>
       <c r="D24" s="40" t="n">
@@ -3731,16 +3728,16 @@
       <c r="E24" s="19" t="n">
         <v>0.053</v>
       </c>
-      <c r="F24" s="49" t="n">
+      <c r="F24" s="48" t="n">
         <v>20.5</v>
       </c>
-      <c r="G24" s="49" t="n">
+      <c r="G24" s="48" t="n">
         <v>22.7</v>
       </c>
-      <c r="H24" s="49" t="n">
+      <c r="H24" s="48" t="n">
         <v>34.5</v>
       </c>
-      <c r="I24" s="49" t="n">
+      <c r="I24" s="48" t="n">
         <v>2.3</v>
       </c>
     </row>
@@ -3753,7 +3750,7 @@
       <c r="B25" s="7" t="n">
         <v>279</v>
       </c>
-      <c r="C25" s="48" t="n">
+      <c r="C25" s="47" t="n">
         <v>0.253</v>
       </c>
       <c r="D25" s="23" t="n">
@@ -3762,16 +3759,16 @@
       <c r="E25" s="36" t="n">
         <v>-0.019</v>
       </c>
-      <c r="F25" s="49" t="n">
+      <c r="F25" s="48" t="n">
         <v>24.4</v>
       </c>
-      <c r="G25" s="49" t="n">
+      <c r="G25" s="48" t="n">
         <v>24.4</v>
       </c>
-      <c r="H25" s="49" t="n">
+      <c r="H25" s="48" t="n">
         <v>43.6</v>
       </c>
-      <c r="I25" s="49" t="n">
+      <c r="I25" s="48" t="n">
         <v>6.7</v>
       </c>
     </row>
@@ -3784,7 +3781,7 @@
       <c r="B26" s="7" t="n">
         <v>112</v>
       </c>
-      <c r="C26" s="48" t="n">
+      <c r="C26" s="47" t="n">
         <v>0.283</v>
       </c>
       <c r="D26" s="23" t="n">
@@ -3793,16 +3790,16 @@
       <c r="E26" s="36" t="n">
         <v>0.004</v>
       </c>
-      <c r="F26" s="49" t="n">
+      <c r="F26" s="48" t="n">
         <v>20.5</v>
       </c>
-      <c r="G26" s="49" t="n">
+      <c r="G26" s="48" t="n">
         <v>22.5</v>
       </c>
-      <c r="H26" s="49" t="n">
+      <c r="H26" s="48" t="n">
         <v>34.6</v>
       </c>
-      <c r="I26" s="49" t="n">
+      <c r="I26" s="48" t="n">
         <v>4.9</v>
       </c>
     </row>
@@ -3815,7 +3812,7 @@
       <c r="B27" s="7" t="n">
         <v>323</v>
       </c>
-      <c r="C27" s="48" t="n">
+      <c r="C27" s="47" t="n">
         <v>0.312</v>
       </c>
       <c r="D27" s="23" t="n">
@@ -3824,16 +3821,16 @@
       <c r="E27" s="36" t="n">
         <v>0.016</v>
       </c>
-      <c r="F27" s="49" t="n">
+      <c r="F27" s="48" t="n">
         <v>19.8</v>
       </c>
-      <c r="G27" s="49" t="n">
+      <c r="G27" s="48" t="n">
         <v>20.9</v>
       </c>
-      <c r="H27" s="49" t="n">
+      <c r="H27" s="48" t="n">
         <v>41.4</v>
       </c>
-      <c r="I27" s="49" t="n">
+      <c r="I27" s="48" t="n">
         <v>5</v>
       </c>
     </row>
@@ -3846,7 +3843,7 @@
       <c r="B28" s="7" t="n">
         <v>56</v>
       </c>
-      <c r="C28" s="48" t="n">
+      <c r="C28" s="47" t="n">
         <v>0.213</v>
       </c>
       <c r="D28" s="33" t="n">
@@ -3855,16 +3852,16 @@
       <c r="E28" s="34" t="n">
         <v>-0.095</v>
       </c>
-      <c r="F28" s="49" t="n">
+      <c r="F28" s="48" t="n">
         <v>23.2</v>
       </c>
-      <c r="G28" s="49" t="n">
+      <c r="G28" s="48" t="n">
         <v>34.4</v>
       </c>
-      <c r="H28" s="49" t="n">
+      <c r="H28" s="48" t="n">
         <v>40.5</v>
       </c>
-      <c r="I28" s="49" t="n">
+      <c r="I28" s="48" t="n">
         <v>5.4</v>
       </c>
     </row>
@@ -3877,7 +3874,7 @@
       <c r="B29" s="7" t="n">
         <v>298</v>
       </c>
-      <c r="C29" s="48" t="n">
+      <c r="C29" s="47" t="n">
         <v>0.318</v>
       </c>
       <c r="D29" s="23" t="n">
@@ -3886,16 +3883,16 @@
       <c r="E29" s="36" t="n">
         <v>0.001</v>
       </c>
-      <c r="F29" s="49" t="n">
+      <c r="F29" s="48" t="n">
         <v>25.8</v>
       </c>
-      <c r="G29" s="49" t="n">
+      <c r="G29" s="48" t="n">
         <v>28.9</v>
       </c>
-      <c r="H29" s="49" t="n">
+      <c r="H29" s="48" t="n">
         <v>46</v>
       </c>
-      <c r="I29" s="49" t="n">
+      <c r="I29" s="48" t="n">
         <v>11</v>
       </c>
     </row>
@@ -3908,7 +3905,7 @@
       <c r="B30" s="7" t="n">
         <v>64</v>
       </c>
-      <c r="C30" s="48" t="n">
+      <c r="C30" s="47" t="n">
         <v>0.315</v>
       </c>
       <c r="D30" s="23" t="n">
@@ -3917,16 +3914,16 @@
       <c r="E30" s="36" t="n">
         <v>-0.003</v>
       </c>
-      <c r="F30" s="49" t="n">
+      <c r="F30" s="48" t="n">
         <v>25</v>
       </c>
-      <c r="G30" s="49" t="n">
+      <c r="G30" s="48" t="n">
         <v>24.8</v>
       </c>
-      <c r="H30" s="49" t="n">
+      <c r="H30" s="48" t="n">
         <v>29.3</v>
       </c>
-      <c r="I30" s="49" t="n">
+      <c r="I30" s="48" t="n">
         <v>12.2</v>
       </c>
     </row>
@@ -3939,7 +3936,7 @@
       <c r="B31" s="7" t="n">
         <v>65</v>
       </c>
-      <c r="C31" s="48" t="n">
+      <c r="C31" s="47" t="n">
         <v>0.292</v>
       </c>
       <c r="D31" s="33" t="n">
@@ -3948,16 +3945,16 @@
       <c r="E31" s="34" t="n">
         <v>-0.029</v>
       </c>
-      <c r="F31" s="49" t="n">
+      <c r="F31" s="48" t="n">
         <v>20</v>
       </c>
-      <c r="G31" s="49" t="n">
+      <c r="G31" s="48" t="n">
         <v>24.6</v>
       </c>
-      <c r="H31" s="49" t="n">
+      <c r="H31" s="48" t="n">
         <v>40</v>
       </c>
-      <c r="I31" s="49" t="n">
+      <c r="I31" s="48" t="n">
         <v>2.2</v>
       </c>
     </row>
@@ -3970,7 +3967,7 @@
       <c r="B32" s="7" t="n">
         <v>271</v>
       </c>
-      <c r="C32" s="48" t="n">
+      <c r="C32" s="47" t="n">
         <v>0.275</v>
       </c>
       <c r="D32" s="33" t="n">
@@ -3979,16 +3976,16 @@
       <c r="E32" s="34" t="n">
         <v>-0.046</v>
       </c>
-      <c r="F32" s="49" t="n">
+      <c r="F32" s="48" t="n">
         <v>25.8</v>
       </c>
-      <c r="G32" s="49" t="n">
+      <c r="G32" s="48" t="n">
         <v>23.5</v>
       </c>
-      <c r="H32" s="49" t="n">
+      <c r="H32" s="48" t="n">
         <v>43.7</v>
       </c>
-      <c r="I32" s="49" t="n">
+      <c r="I32" s="48" t="n">
         <v>10.5</v>
       </c>
     </row>
@@ -4001,7 +3998,7 @@
       <c r="B33" s="7" t="n">
         <v>99</v>
       </c>
-      <c r="C33" s="48" t="n">
+      <c r="C33" s="47" t="n">
         <v>0.312</v>
       </c>
       <c r="D33" s="23" t="n">
@@ -4010,16 +4007,16 @@
       <c r="E33" s="36" t="n">
         <v>-0.011</v>
       </c>
-      <c r="F33" s="49" t="n">
+      <c r="F33" s="48" t="n">
         <v>35.4</v>
       </c>
-      <c r="G33" s="49" t="n">
+      <c r="G33" s="48" t="n">
         <v>42.6</v>
       </c>
-      <c r="H33" s="49" t="n">
+      <c r="H33" s="48" t="n">
         <v>46.4</v>
       </c>
-      <c r="I33" s="49" t="n">
+      <c r="I33" s="48" t="n">
         <v>12.5</v>
       </c>
     </row>
@@ -4032,7 +4029,7 @@
       <c r="B34" s="7" t="n">
         <v>111</v>
       </c>
-      <c r="C34" s="48" t="n">
+      <c r="C34" s="47" t="n">
         <v>0.349</v>
       </c>
       <c r="D34" s="40" t="n">
@@ -4041,16 +4038,16 @@
       <c r="E34" s="19" t="n">
         <v>0.023</v>
       </c>
-      <c r="F34" s="49" t="n">
+      <c r="F34" s="48" t="n">
         <v>16.2</v>
       </c>
-      <c r="G34" s="49" t="n">
+      <c r="G34" s="48" t="n">
         <v>21.4</v>
       </c>
-      <c r="H34" s="49" t="n">
+      <c r="H34" s="48" t="n">
         <v>37.5</v>
       </c>
-      <c r="I34" s="49" t="n">
+      <c r="I34" s="48" t="n">
         <v>8.800000000000001</v>
       </c>
     </row>
@@ -4063,7 +4060,7 @@
       <c r="B35" s="7" t="n">
         <v>118</v>
       </c>
-      <c r="C35" s="48" t="n">
+      <c r="C35" s="47" t="n">
         <v>0.32</v>
       </c>
       <c r="D35" s="23" t="n">
@@ -4072,16 +4069,16 @@
       <c r="E35" s="36" t="n">
         <v>-0.01</v>
       </c>
-      <c r="F35" s="49" t="n">
+      <c r="F35" s="48" t="n">
         <v>21.2</v>
       </c>
-      <c r="G35" s="49" t="n">
+      <c r="G35" s="48" t="n">
         <v>21.8</v>
       </c>
-      <c r="H35" s="49" t="n">
+      <c r="H35" s="48" t="n">
         <v>41.5</v>
       </c>
-      <c r="I35" s="49" t="n">
+      <c r="I35" s="48" t="n">
         <v>8.5</v>
       </c>
     </row>
@@ -4094,7 +4091,7 @@
       <c r="B36" s="7" t="n">
         <v>29</v>
       </c>
-      <c r="C36" s="48" t="n">
+      <c r="C36" s="47" t="n">
         <v>0.251</v>
       </c>
       <c r="D36" s="33" t="n">
@@ -4103,16 +4100,16 @@
       <c r="E36" s="34" t="n">
         <v>-0.096</v>
       </c>
-      <c r="F36" s="49" t="n">
+      <c r="F36" s="48" t="n">
         <v>13.8</v>
       </c>
-      <c r="G36" s="49" t="n">
+      <c r="G36" s="48" t="n">
         <v>14.9</v>
       </c>
-      <c r="H36" s="49" t="n">
+      <c r="H36" s="48" t="n">
         <v>21.1</v>
       </c>
-      <c r="I36" s="49" t="n">
+      <c r="I36" s="48" t="n">
         <v>5.3</v>
       </c>
     </row>
@@ -4125,7 +4122,7 @@
       <c r="B37" s="7" t="n">
         <v>250</v>
       </c>
-      <c r="C37" s="48" t="n">
+      <c r="C37" s="47" t="n">
         <v>0.343</v>
       </c>
       <c r="D37" s="23" t="n">
@@ -4134,16 +4131,16 @@
       <c r="E37" s="36" t="n">
         <v>-0.008</v>
       </c>
-      <c r="F37" s="49" t="n">
+      <c r="F37" s="48" t="n">
         <v>22.4</v>
       </c>
-      <c r="G37" s="49" t="n">
+      <c r="G37" s="48" t="n">
         <v>26</v>
       </c>
-      <c r="H37" s="49" t="n">
+      <c r="H37" s="48" t="n">
         <v>48.5</v>
       </c>
-      <c r="I37" s="49" t="n">
+      <c r="I37" s="48" t="n">
         <v>10.8</v>
       </c>
     </row>
@@ -4156,7 +4153,7 @@
       <c r="B38" s="7" t="n">
         <v>70</v>
       </c>
-      <c r="C38" s="48" t="n">
+      <c r="C38" s="47" t="n">
         <v>0.382</v>
       </c>
       <c r="D38" s="33" t="n">
@@ -4165,16 +4162,16 @@
       <c r="E38" s="34" t="n">
         <v>-0.026</v>
       </c>
-      <c r="F38" s="49" t="n">
+      <c r="F38" s="48" t="n">
         <v>21.4</v>
       </c>
-      <c r="G38" s="49" t="n">
+      <c r="G38" s="48" t="n">
         <v>30</v>
       </c>
-      <c r="H38" s="49" t="n">
+      <c r="H38" s="48" t="n">
         <v>46.3</v>
       </c>
-      <c r="I38" s="49" t="n">
+      <c r="I38" s="48" t="n">
         <v>12.5</v>
       </c>
     </row>
@@ -4251,7 +4248,7 @@
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="50" t="inlineStr">
+      <c r="A3" s="49" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -4274,19 +4271,19 @@
           <t>22/30</t>
         </is>
       </c>
-      <c r="F3" s="51" t="inlineStr">
+      <c r="F3" s="50" t="inlineStr">
         <is>
           <t>→ External</t>
         </is>
       </c>
-      <c r="G3" s="52" t="inlineStr">
+      <c r="G3" s="51" t="inlineStr">
         <is>
           <t>Donovan + Raleigh returning — run production will improve</t>
         </is>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="50" t="inlineStr">
+      <c r="A4" s="49" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -4314,14 +4311,14 @@
           <t>✓ Yes</t>
         </is>
       </c>
-      <c r="G4" s="52" t="inlineStr">
+      <c r="G4" s="51" t="inlineStr">
         <is>
           <t>Raleigh returns from IL — fixes this immediately</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="50" t="inlineStr">
+      <c r="A5" s="49" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -4349,14 +4346,14 @@
           <t>✓ Yes</t>
         </is>
       </c>
-      <c r="G5" s="52" t="inlineStr">
+      <c r="G5" s="51" t="inlineStr">
         <is>
           <t>Crawford returns from IL — .354 xwOBA, elite OBP</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="50" t="inlineStr">
+      <c r="A6" s="49" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -4379,19 +4376,19 @@
           <t>25/30</t>
         </is>
       </c>
-      <c r="F6" s="51" t="inlineStr">
+      <c r="F6" s="50" t="inlineStr">
         <is>
           <t>→ External</t>
         </is>
       </c>
-      <c r="G6" s="52" t="inlineStr">
+      <c r="G6" s="51" t="inlineStr">
         <is>
           <t>Contact rate improving — Crawford return helps</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="50" t="inlineStr">
+      <c r="A7" s="49" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -4414,19 +4411,19 @@
           <t>25/30</t>
         </is>
       </c>
-      <c r="F7" s="51" t="inlineStr">
+      <c r="F7" s="50" t="inlineStr">
         <is>
           <t>→ External</t>
         </is>
       </c>
-      <c r="G7" s="52" t="inlineStr">
+      <c r="G7" s="51" t="inlineStr">
         <is>
           <t>Full health lineup projects top 5 AL — internal fix available</t>
         </is>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="50" t="inlineStr">
+      <c r="A8" s="49" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -4449,19 +4446,19 @@
           <t>26/30</t>
         </is>
       </c>
-      <c r="F8" s="51" t="inlineStr">
+      <c r="F8" s="50" t="inlineStr">
         <is>
           <t>→ External</t>
         </is>
       </c>
-      <c r="G8" s="52" t="inlineStr">
+      <c r="G8" s="51" t="inlineStr">
         <is>
           <t>Three true outcomes team — by design, power offsets BA</t>
         </is>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="50" t="inlineStr">
+      <c r="A9" s="49" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -4484,19 +4481,19 @@
           <t>27/30</t>
         </is>
       </c>
-      <c r="F9" s="51" t="inlineStr">
+      <c r="F9" s="50" t="inlineStr">
         <is>
           <t>→ External</t>
         </is>
       </c>
-      <c r="G9" s="52" t="inlineStr">
+      <c r="G9" s="51" t="inlineStr">
         <is>
           <t>Raley 19.2 Barrel% + Raleigh power returning — SLG improving</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="50" t="inlineStr">
+      <c r="A10" s="49" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -4519,19 +4516,19 @@
           <t>28/30</t>
         </is>
       </c>
-      <c r="F10" s="51" t="inlineStr">
+      <c r="F10" s="50" t="inlineStr">
         <is>
           <t>→ External</t>
         </is>
       </c>
-      <c r="G10" s="52" t="inlineStr">
+      <c r="G10" s="51" t="inlineStr">
         <is>
           <t>Naylor below average — potential deadline upgrade target</t>
         </is>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="53" t="inlineStr">
+      <c r="A11" s="52" t="inlineStr">
         <is>
           <t>MONITOR</t>
         </is>
@@ -4559,14 +4556,14 @@
           <t>✓ Yes</t>
         </is>
       </c>
-      <c r="G11" s="54" t="inlineStr">
+      <c r="G11" s="53" t="inlineStr">
         <is>
           <t>Error rate acceptable — Crawford return stabilizes SS</t>
         </is>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="53" t="inlineStr">
+      <c r="A12" s="52" t="inlineStr">
         <is>
           <t>MONITOR</t>
         </is>
@@ -4594,14 +4591,14 @@
           <t>✓ Yes</t>
         </is>
       </c>
-      <c r="G12" s="54" t="inlineStr">
+      <c r="G12" s="53" t="inlineStr">
         <is>
           <t>Outfield defense solid — Robles return improves range</t>
         </is>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="53" t="inlineStr">
+      <c r="A13" s="52" t="inlineStr">
         <is>
           <t>MONITOR</t>
         </is>
@@ -4624,19 +4621,19 @@
           <t>18/30</t>
         </is>
       </c>
-      <c r="F13" s="51" t="inlineStr">
+      <c r="F13" s="50" t="inlineStr">
         <is>
           <t>→ External</t>
         </is>
       </c>
-      <c r="G13" s="54" t="inlineStr">
+      <c r="G13" s="53" t="inlineStr">
         <is>
           <t>Improving with IL returns — no external move needed</t>
         </is>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="53" t="inlineStr">
+      <c r="A14" s="52" t="inlineStr">
         <is>
           <t>MONITOR</t>
         </is>
@@ -4664,14 +4661,14 @@
           <t>✓ Yes</t>
         </is>
       </c>
-      <c r="G14" s="54" t="inlineStr">
+      <c r="G14" s="53" t="inlineStr">
         <is>
           <t>Donovan returns from IL — .839 OPS when healthy</t>
         </is>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="53" t="inlineStr">
+      <c r="A15" s="52" t="inlineStr">
         <is>
           <t>MONITOR</t>
         </is>
@@ -4694,19 +4691,19 @@
           <t>19/30</t>
         </is>
       </c>
-      <c r="F15" s="51" t="inlineStr">
+      <c r="F15" s="50" t="inlineStr">
         <is>
           <t>→ External</t>
         </is>
       </c>
-      <c r="G15" s="54" t="inlineStr">
+      <c r="G15" s="53" t="inlineStr">
         <is>
           <t>Power is fine — high K rate suppressing batting avg</t>
         </is>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="53" t="inlineStr">
+      <c r="A16" s="52" t="inlineStr">
         <is>
           <t>MONITOR</t>
         </is>
@@ -4734,14 +4731,14 @@
           <t>✓ Yes</t>
         </is>
       </c>
-      <c r="G16" s="54" t="inlineStr">
+      <c r="G16" s="53" t="inlineStr">
         <is>
           <t>Crawford 14.7 BB% returning — OBP will jump immediately</t>
         </is>
       </c>
     </row>
     <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="53" t="inlineStr">
+      <c r="A17" s="52" t="inlineStr">
         <is>
           <t>MONITOR</t>
         </is>
@@ -4769,14 +4766,14 @@
           <t>✓ Yes</t>
         </is>
       </c>
-      <c r="G17" s="54" t="inlineStr">
+      <c r="G17" s="53" t="inlineStr">
         <is>
           <t>Naylor -0.7 DWAR at 1B — biggest defensive hole on roster</t>
         </is>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="53" t="inlineStr">
+      <c r="A18" s="52" t="inlineStr">
         <is>
           <t>MONITOR</t>
         </is>
@@ -4799,19 +4796,19 @@
           <t>19/30</t>
         </is>
       </c>
-      <c r="F18" s="51" t="inlineStr">
+      <c r="F18" s="50" t="inlineStr">
         <is>
           <t>→ External</t>
         </is>
       </c>
-      <c r="G18" s="54" t="inlineStr">
+      <c r="G18" s="53" t="inlineStr">
         <is>
           <t>Raley + Canzone solid — Refsnyder/Robles dragged WAR down</t>
         </is>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="53" t="inlineStr">
+      <c r="A19" s="52" t="inlineStr">
         <is>
           <t>MONITOR</t>
         </is>
@@ -4834,12 +4831,12 @@
           <t>20/30</t>
         </is>
       </c>
-      <c r="F19" s="51" t="inlineStr">
+      <c r="F19" s="50" t="inlineStr">
         <is>
           <t>→ External</t>
         </is>
       </c>
-      <c r="G19" s="54" t="inlineStr">
+      <c r="G19" s="53" t="inlineStr">
         <is>
           <t>RISP production improves with Donovan + Raleigh returning</t>
         </is>
@@ -4859,7 +4856,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D44"/>
+  <dimension ref="A1:D43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4905,7 +4902,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="50" t="inlineStr">
+      <c r="A4" s="49" t="inlineStr">
         <is>
           <t>IMMEDIATE</t>
         </is>
@@ -4927,7 +4924,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="50" t="inlineStr">
+      <c r="A5" s="49" t="inlineStr">
         <is>
           <t>IMMEDIATE</t>
         </is>
@@ -4949,7 +4946,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="50" t="inlineStr">
+      <c r="A6" s="49" t="inlineStr">
         <is>
           <t>IMMEDIATE</t>
         </is>
@@ -4971,7 +4968,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="50" t="inlineStr">
+      <c r="A7" s="49" t="inlineStr">
         <is>
           <t>IMMEDIATE</t>
         </is>
@@ -4993,7 +4990,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="50" t="inlineStr">
+      <c r="A8" s="49" t="inlineStr">
         <is>
           <t>IMMEDIATE</t>
         </is>
@@ -5015,7 +5012,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="50" t="inlineStr">
+      <c r="A9" s="49" t="inlineStr">
         <is>
           <t>IMMEDIATE</t>
         </is>
@@ -5037,51 +5034,51 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="50" t="inlineStr">
+      <c r="A10" s="54" t="inlineStr">
+        <is>
+          <t>SOON</t>
+        </is>
+      </c>
+      <c r="B10" s="50" t="inlineStr">
+        <is>
+          <t>PIGGYBACK</t>
+        </is>
+      </c>
+      <c r="C10" s="55" t="inlineStr">
+        <is>
+          <t>George Kirby</t>
+        </is>
+      </c>
+      <c r="D10" s="56" t="inlineStr">
+        <is>
+          <t>Monitor — K rate declined, piggyback with Miller</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="49" t="inlineStr">
         <is>
           <t>IMMEDIATE</t>
         </is>
       </c>
-      <c r="B10" s="32" t="inlineStr">
-        <is>
-          <t>DFA</t>
-        </is>
-      </c>
-      <c r="C10" s="30" t="inlineStr">
-        <is>
-          <t>Michael Rucker</t>
-        </is>
-      </c>
-      <c r="D10" s="31" t="inlineStr">
-        <is>
-          <t>below replacement level</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="55" t="inlineStr">
-        <is>
-          <t>SOON</t>
-        </is>
-      </c>
-      <c r="B11" s="51" t="inlineStr">
-        <is>
-          <t>PIGGYBACK</t>
-        </is>
-      </c>
-      <c r="C11" s="56" t="inlineStr">
-        <is>
-          <t>George Kirby</t>
-        </is>
-      </c>
-      <c r="D11" s="57" t="inlineStr">
-        <is>
-          <t>Monitor — K rate declined, piggyback with Miller</t>
+      <c r="B11" s="32" t="inlineStr">
+        <is>
+          <t>ROLE CHANGE</t>
+        </is>
+      </c>
+      <c r="C11" s="30" t="inlineStr">
+        <is>
+          <t>Andrés Muñoz</t>
+        </is>
+      </c>
+      <c r="D11" s="31" t="inlineStr">
+        <is>
+          <t>Role change — move to setup, Brash to close</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="50" t="inlineStr">
+      <c r="A12" s="49" t="inlineStr">
         <is>
           <t>IMMEDIATE</t>
         </is>
@@ -5093,284 +5090,262 @@
       </c>
       <c r="C12" s="30" t="inlineStr">
         <is>
-          <t>Andrés Muñoz</t>
+          <t>Matt Brash (15-day IL)</t>
         </is>
       </c>
       <c r="D12" s="31" t="inlineStr">
         <is>
-          <t>Role change — move to setup, Brash to close</t>
+          <t>Promote to closer — 0.60 ERA, elite</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="50" t="inlineStr">
-        <is>
-          <t>IMMEDIATE</t>
-        </is>
-      </c>
-      <c r="B13" s="32" t="inlineStr">
-        <is>
-          <t>ROLE CHANGE</t>
-        </is>
-      </c>
-      <c r="C13" s="30" t="inlineStr">
-        <is>
-          <t>Matt Brash (15-day IL)</t>
-        </is>
-      </c>
-      <c r="D13" s="31" t="inlineStr">
-        <is>
-          <t>Promote to closer — 0.60 ERA, elite</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="53" t="inlineStr">
+      <c r="A13" s="52" t="inlineStr">
         <is>
           <t>WHEN READY</t>
         </is>
       </c>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t>ACTIVATE</t>
         </is>
       </c>
-      <c r="C14" s="15" t="inlineStr">
+      <c r="C13" s="15" t="inlineStr">
         <is>
           <t>Brendan Donovan (10-day IL)</t>
         </is>
       </c>
-      <c r="D14" s="16" t="inlineStr">
+      <c r="D13" s="16" t="inlineStr">
         <is>
           <t>Returning from IL — key contributor</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>DEADLINE STRATEGY</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="40" customHeight="1">
-      <c r="A17" s="58" t="inlineStr">
+    <row r="16" ht="40" customHeight="1">
+      <c r="A16" s="57" t="inlineStr">
         <is>
           <t>Minor buyer — rotation top 5 MLB, bullpen elite with Brash, offense improving with IL returns. Stand pat or add depth only. Do NOT trade prospects for win-now pieces — system too valuable.</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>DEADLINE TARGETS</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="21" t="inlineStr">
+        <is>
+          <t>Position</t>
+        </is>
+      </c>
+      <c r="B19" s="58" t="inlineStr">
+        <is>
+          <t>1B or DH</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="21" t="inlineStr">
         <is>
-          <t>Position</t>
-        </is>
-      </c>
-      <c r="B20" s="59" t="inlineStr">
-        <is>
-          <t>1B or DH</t>
+          <t>Profile</t>
+        </is>
+      </c>
+      <c r="B20" s="58" t="inlineStr">
+        <is>
+          <t>Contact/power hybrid — .270+ BA, 20+ HR pace, .340+ xwOBA</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="21" t="inlineStr">
         <is>
-          <t>Profile</t>
-        </is>
-      </c>
-      <c r="B21" s="59" t="inlineStr">
-        <is>
-          <t>Contact/power hybrid — .270+ BA, 20+ HR pace, .340+ xwOBA</t>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="B21" s="58" t="inlineStr">
+        <is>
+          <t>Low-mid prospect or waiver claim</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="21" t="inlineStr">
         <is>
-          <t>Cost</t>
-        </is>
-      </c>
-      <c r="B22" s="59" t="inlineStr">
-        <is>
-          <t>Low-mid prospect or waiver claim</t>
+          <t>Urgency</t>
+        </is>
+      </c>
+      <c r="B22" s="58" t="inlineStr">
+        <is>
+          <t>By July 31</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="21" t="inlineStr">
         <is>
-          <t>Urgency</t>
-        </is>
-      </c>
-      <c r="B23" s="59" t="inlineStr">
-        <is>
-          <t>By July 31</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="21" t="inlineStr">
-        <is>
           <t>Why</t>
         </is>
       </c>
-      <c r="B24" s="59" t="inlineStr">
+      <c r="B23" s="58" t="inlineStr">
         <is>
           <t>1B WAR rank 28-30/30 — Naylor below average bat and glove</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="21" t="inlineStr">
+        <is>
+          <t>Position</t>
+        </is>
+      </c>
+      <c r="B25" s="58" t="inlineStr">
+        <is>
+          <t>RP</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="21" t="inlineStr">
         <is>
-          <t>Position</t>
-        </is>
-      </c>
-      <c r="B26" s="59" t="inlineStr">
-        <is>
-          <t>RP</t>
+          <t>Profile</t>
+        </is>
+      </c>
+      <c r="B26" s="58" t="inlineStr">
+        <is>
+          <t>Veteran middle reliever — command-first, groundball tendency</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="21" t="inlineStr">
         <is>
-          <t>Profile</t>
-        </is>
-      </c>
-      <c r="B27" s="59" t="inlineStr">
-        <is>
-          <t>Veteran middle reliever — command-first, groundball tendency</t>
+          <t>Cost</t>
+        </is>
+      </c>
+      <c r="B27" s="58" t="inlineStr">
+        <is>
+          <t>Waiver claim or minimum salary</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="21" t="inlineStr">
         <is>
-          <t>Cost</t>
-        </is>
-      </c>
-      <c r="B28" s="59" t="inlineStr">
-        <is>
-          <t>Waiver claim or minimum salary</t>
+          <t>Urgency</t>
+        </is>
+      </c>
+      <c r="B28" s="58" t="inlineStr">
+        <is>
+          <t>Immediate — Hoppe/Wilcox DFA leaves depth hole</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="21" t="inlineStr">
         <is>
-          <t>Urgency</t>
-        </is>
-      </c>
-      <c r="B29" s="59" t="inlineStr">
-        <is>
-          <t>Immediate — Hoppe/Wilcox DFA leaves depth hole</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="21" t="inlineStr">
-        <is>
           <t>Why</t>
         </is>
       </c>
-      <c r="B30" s="59" t="inlineStr">
+      <c r="B29" s="58" t="inlineStr">
         <is>
           <t>Need reliable 6th/7th inning arm behind Ferrer/Bazardo/Speier</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="12" t="inlineStr">
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="12" t="inlineStr">
         <is>
           <t>DO NOT TRADE</t>
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="59" t="inlineStr">
+        <is>
+          <t>✗  Julio Rodriguez    — 10yr/$210M franchise player</t>
+        </is>
+      </c>
+    </row>
     <row r="33">
-      <c r="A33" s="60" t="inlineStr">
-        <is>
-          <t>✗  Julio Rodriguez    — 10yr/$210M franchise player</t>
+      <c r="A33" s="59" t="inlineStr">
+        <is>
+          <t>✗  Bryce Miller       — xwOBA .221 top 3% MLB, ascending</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="60" t="inlineStr">
-        <is>
-          <t>✗  Bryce Miller       — xwOBA .221 top 3% MLB, ascending</t>
+      <c r="A34" s="59" t="inlineStr">
+        <is>
+          <t>✗  Emerson Hancock    — 2.74 ERA, elite rotation piece</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="60" t="inlineStr">
-        <is>
-          <t>✗  Emerson Hancock    — 2.74 ERA, elite rotation piece</t>
+      <c r="A35" s="59" t="inlineStr">
+        <is>
+          <t>✗  Bryan Woo          — xwOBA .272, above average</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="60" t="inlineStr">
-        <is>
-          <t>✗  Bryan Woo          — xwOBA .272, above average</t>
+      <c r="A36" s="59" t="inlineStr">
+        <is>
+          <t>✗  Randy Arozarena    — best bat on team when healthy</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="60" t="inlineStr">
-        <is>
-          <t>✗  Randy Arozarena    — best bat on team when healthy</t>
+      <c r="A37" s="59" t="inlineStr">
+        <is>
+          <t>✗  Matt Brash         — 0.60 ERA, elite closer</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="60" t="inlineStr">
-        <is>
-          <t>✗  Matt Brash         — 0.60 ERA, elite closer</t>
+      <c r="A38" s="59" t="inlineStr">
+        <is>
+          <t>✗  Colt Emerson       — 8yr/$95M franchise cornerstone</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="60" t="inlineStr">
-        <is>
-          <t>✗  Colt Emerson       — 8yr/$95M franchise cornerstone</t>
+      <c r="A39" s="59" t="inlineStr">
+        <is>
+          <t>✗  Cole Young         — 2.4 WAR, emerging star</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="60" t="inlineStr">
-        <is>
-          <t>✗  Cole Young         — 2.4 WAR, emerging star</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="60" t="inlineStr">
+      <c r="A40" s="59" t="inlineStr">
         <is>
           <t>✗  Logan Gilbert      — 3.29 ERA, 2.1 WAR, ascending</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="20" customHeight="1">
-      <c r="A43" s="61" t="inlineStr">
+    <row r="42" ht="20" customHeight="1">
+      <c r="A42" s="60" t="inlineStr">
         <is>
           <t>SELL CANDIDATES</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="30" customHeight="1">
-      <c r="A44" s="15" t="inlineStr">
+    <row r="43" ht="30" customHeight="1">
+      <c r="A43" s="15" t="inlineStr">
         <is>
           <t>Luis Castillo</t>
         </is>
       </c>
-      <c r="B44" s="54" t="inlineStr">
+      <c r="B43" s="53" t="inlineStr">
         <is>
           <t>ERA 5.00+, expensive contract, rotation 6-deep without him  |  Note: Only if ERA continues above 4.50 through July</t>
         </is>
@@ -5378,32 +5353,32 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="A17:D17"/>
     <mergeCell ref="B23:D23"/>
     <mergeCell ref="A35:D35"/>
     <mergeCell ref="A38:D38"/>
-    <mergeCell ref="A43:D43"/>
-    <mergeCell ref="B44:D44"/>
-    <mergeCell ref="A19:D19"/>
     <mergeCell ref="B29:D29"/>
     <mergeCell ref="B28:D28"/>
     <mergeCell ref="A40:D40"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
     <mergeCell ref="A34:D34"/>
     <mergeCell ref="A39:D39"/>
-    <mergeCell ref="B30:D30"/>
-    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A15:D15"/>
     <mergeCell ref="A36:D36"/>
     <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="B43:D43"/>
     <mergeCell ref="B26:D26"/>
-    <mergeCell ref="A41:D41"/>
     <mergeCell ref="A16:D16"/>
+    <mergeCell ref="B25:D25"/>
     <mergeCell ref="A37:D37"/>
+    <mergeCell ref="A18:D18"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="B27:D27"/>
     <mergeCell ref="B21:D21"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A42:D42"/>
     <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
